--- a/examples/HFP_jordan+taylor-qcd.xlsx
+++ b/examples/HFP_jordan+taylor-qcd.xlsx
@@ -3212,8 +3212,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3251,6 +3255,11 @@
           <t>rate</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>property</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="b">
@@ -3277,6 +3286,11 @@
       </c>
       <c r="G2" t="n">
         <v>4</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Lake house</t>
+        </is>
       </c>
     </row>
   </sheetData>
